--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1357142857142857</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1418439716312057</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="D2">
-        <v>0.8642857142857143</v>
+        <v>0.704225352112676</v>
       </c>
       <c r="E2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2957746478873239</v>
+        <v>0.2785714285714286</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2957746478873239</v>
+        <v>0.2887323943661972</v>
       </c>
       <c r="D2">
-        <v>0.704225352112676</v>
+        <v>0.7214285714285714</v>
       </c>
       <c r="E2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
